--- a/outputs/019fc439-d617-7783-a9b4-5347c2d0bf25/GameContent_Perks_Worldbosses_with_Scenes.xlsx
+++ b/outputs/019fc439-d617-7783-a9b4-5347c2d0bf25/GameContent_Perks_Worldbosses_with_Scenes.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R90a016cf443c4b37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="2" r:id="R4aeaea5cd8f34e43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bosses" sheetId="3" r:id="R82f34d189b594434"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Minions" sheetId="4" r:id="Re315a664fb7d4e1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weapons" sheetId="5" r:id="R754ec64be23d40ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armor" sheetId="6" r:id="Rc91994e967fe4636"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpecialItems" sheetId="7" r:id="R40c1283c62db4c99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="8" r:id="Rbebbb7599e3240fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RandomEvents" sheetId="9" r:id="Rdaf7934f72324a43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="10" r:id="R63946441410e476a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WorldBosses" sheetId="11" r:id="R746c8243db70409b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Perks" sheetId="13" r:id="R6e26a05292fc468f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contracts" sheetId="14" r:id="R12e122eb7e424ab9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenes" sheetId="15" r:id="Rb07bc4dda674430d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SceneChoices" sheetId="16" r:id="R85bdd64d30a24d84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R691c3caa447a4a4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="2" r:id="R5acb8e927b1745ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bosses" sheetId="3" r:id="R49b0c618f364419f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Minions" sheetId="4" r:id="Rf95f2fefae2f4b63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weapons" sheetId="5" r:id="Rb93a3617307148c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armor" sheetId="6" r:id="R1d6630298f374690"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpecialItems" sheetId="7" r:id="Rd91e78cdeeb644d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="8" r:id="R7e919b7ea3ae4c9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RandomEvents" sheetId="9" r:id="R089250bda95e4fbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="10" r:id="R18fe6d17436d49f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WorldBosses" sheetId="11" r:id="Ra9f450b39dcf4ca5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Perks" sheetId="13" r:id="Re1181d775e114c1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contracts" sheetId="14" r:id="R3519dfc81354488d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenes" sheetId="15" r:id="R4177e7119ba84ac0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SceneChoices" sheetId="16" r:id="R061f69402c6f453b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,7 +519,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ScenesTable" displayName="ScenesTable" ref="A1:T35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ScenesTable" displayName="ScenesTable" ref="A1:T52" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="20">
     <x:tableColumn id="1" name="SceneKey"/>
     <x:tableColumn id="2" name="MovieName"/>
@@ -547,7 +547,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SceneChoicesTable" displayName="SceneChoicesTable" ref="A1:P171" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SceneChoicesTable" displayName="SceneChoicesTable" ref="A1:P256" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="16">
     <x:tableColumn id="1" name="SceneKey"/>
     <x:tableColumn id="2" name="ChoiceKey"/>
@@ -8378,10 +8378,1064 @@
         <x:v>Late-game arena Scene against the Harkonnen champion.</x:v>
       </x:c>
     </x:row>
+    <x:row r="36" ht="48" customHeight="1">
+      <x:c r="A36" s="66" t="str">
+        <x:v>TOTALRECALL_REKALL_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B36" s="66" t="str">
+        <x:v>Total Recall</x:v>
+      </x:c>
+      <x:c r="C36" s="66" t="str">
+        <x:v>Ambush at Rekall</x:v>
+      </x:c>
+      <x:c r="D36" s="66" t="str">
+        <x:v>Emergency lights flash through the memory clinic as security shutters close. Douglas Quaid searches for an exit while Richter advances through the procedure rooms with a pistol drawn.</x:v>
+      </x:c>
+      <x:c r="E36" s="66" t="str">
+        <x:v>Douglas Quaid</x:v>
+      </x:c>
+      <x:c r="F36" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G36" s="66" t="str">
+        <x:v>Richter</x:v>
+      </x:c>
+      <x:c r="H36" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I36" s="73" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J36" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K36" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L36" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M36" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N36" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O36" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P36" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q36" s="73" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="R36" s="73" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="S36" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T36" s="66" t="str">
+        <x:v>Minion Scene combining uncertain memories with a clinic pursuit.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="48" customHeight="1">
+      <x:c r="A37" s="66" t="str">
+        <x:v>STARTREKVI_CONSPIRACY</x:v>
+      </x:c>
+      <x:c r="B37" s="66" t="str">
+        <x:v>Star Trek VI: The Undiscovered Country</x:v>
+      </x:c>
+      <x:c r="C37" s="66" t="str">
+        <x:v>Conspiracy on Deck Six</x:v>
+      </x:c>
+      <x:c r="D37" s="66" t="str">
+        <x:v>A phaser alarm sounds through an empty corridor while sealed orders appear on the wall terminal. James T. Kirk follows the evidence as Valeris steps from the turbolift with a disruptor.</x:v>
+      </x:c>
+      <x:c r="E37" s="66" t="str">
+        <x:v>James T. Kirk</x:v>
+      </x:c>
+      <x:c r="F37" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G37" s="66" t="str">
+        <x:v>Valeris</x:v>
+      </x:c>
+      <x:c r="H37" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I37" s="73" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J37" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K37" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L37" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M37" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N37" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O37" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P37" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q37" s="73" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="R37" s="73" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="S37" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T37" s="66" t="str">
+        <x:v>Investigation Scene aboard the Enterprise.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="48" customHeight="1">
+      <x:c r="A38" s="66" t="str">
+        <x:v>THREEHUNDRED_IMMORTAL_NIGHT</x:v>
+      </x:c>
+      <x:c r="B38" s="66" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C38" s="66" t="str">
+        <x:v>Immortals in the Dark</x:v>
+      </x:c>
+      <x:c r="D38" s="66" t="str">
+        <x:v>The moon disappears behind smoke as masked warriors climb over the bodies at the pass. Leonidas lowers his spear while a Persian Immortal moves silently toward the broken shield wall.</x:v>
+      </x:c>
+      <x:c r="E38" s="66" t="str">
+        <x:v>Leonidas</x:v>
+      </x:c>
+      <x:c r="F38" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G38" s="66" t="str">
+        <x:v>Persian Immortal</x:v>
+      </x:c>
+      <x:c r="H38" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I38" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J38" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K38" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L38" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M38" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N38" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O38" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P38" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q38" s="73" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="R38" s="73" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="S38" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T38" s="66" t="str">
+        <x:v>Night assault by Xerxes's elite minion.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="48" customHeight="1">
+      <x:c r="A39" s="66" t="str">
+        <x:v>T2_FREEWAY_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B39" s="66" t="str">
+        <x:v>Terminator 2: Judgment Day</x:v>
+      </x:c>
+      <x:c r="C39" s="66" t="str">
+        <x:v>Endoskeleton on the Freeway</x:v>
+      </x:c>
+      <x:c r="D39" s="66" t="str">
+        <x:v>Abandoned vehicles burn beneath the overpass as mechanical footsteps echo through the smoke. Sarah Connor checks her weapon while a T-800 Endoskeleton advances between the wrecks.</x:v>
+      </x:c>
+      <x:c r="E39" s="66" t="str">
+        <x:v>Sarah Connor</x:v>
+      </x:c>
+      <x:c r="F39" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G39" s="66" t="str">
+        <x:v>T-800 Endoskeleton</x:v>
+      </x:c>
+      <x:c r="H39" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I39" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J39" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K39" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L39" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M39" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N39" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O39" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P39" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q39" s="73" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="R39" s="73" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="S39" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T39" s="66" t="str">
+        <x:v>Future-war minion encounter on a ruined freeway.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="48" customHeight="1">
+      <x:c r="A40" s="66" t="str">
+        <x:v>TWOTOWERS_DEEPING_BREACH</x:v>
+      </x:c>
+      <x:c r="B40" s="66" t="str">
+        <x:v>The Lord of the Rings: The Two Towers</x:v>
+      </x:c>
+      <x:c r="C40" s="66" t="str">
+        <x:v>Breach at the Deeping Wall</x:v>
+      </x:c>
+      <x:c r="D40" s="66" t="str">
+        <x:v>Rain lashes the fortress as ladders rise against the stone. Aragorn reaches the shattered parapet while an Uruk-hai Berserker charges through the smoke.</x:v>
+      </x:c>
+      <x:c r="E40" s="66" t="str">
+        <x:v>Aragorn</x:v>
+      </x:c>
+      <x:c r="F40" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G40" s="66" t="str">
+        <x:v>Uruk-hai Berserker</x:v>
+      </x:c>
+      <x:c r="H40" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I40" s="73" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J40" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K40" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L40" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M40" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N40" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O40" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P40" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q40" s="73" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="R40" s="73" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="S40" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T40" s="66" t="str">
+        <x:v>Helm's Deep minion Scene.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="48" customHeight="1">
+      <x:c r="A41" s="66" t="str">
+        <x:v>MATRIX_ROOFTOP_AGENT</x:v>
+      </x:c>
+      <x:c r="B41" s="66" t="str">
+        <x:v>The Matrix</x:v>
+      </x:c>
+      <x:c r="C41" s="66" t="str">
+        <x:v>Agent on the Rooftop</x:v>
+      </x:c>
+      <x:c r="D41" s="66" t="str">
+        <x:v>Helicopter rotors beat against a glass tower while green code ripples across the skyline. Neo reaches the roof as Agent Jones takes control of a nearby guard.</x:v>
+      </x:c>
+      <x:c r="E41" s="66" t="str">
+        <x:v>Neo</x:v>
+      </x:c>
+      <x:c r="F41" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G41" s="66" t="str">
+        <x:v>Agent Jones</x:v>
+      </x:c>
+      <x:c r="H41" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I41" s="73" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J41" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K41" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L41" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M41" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N41" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O41" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P41" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q41" s="73" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="R41" s="73" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="S41" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T41" s="66" t="str">
+        <x:v>Rooftop minion confrontation inside the Matrix.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="48" customHeight="1">
+      <x:c r="A42" s="66" t="str">
+        <x:v>GLADIATOR_TIGRIS_ARENA</x:v>
+      </x:c>
+      <x:c r="B42" s="66" t="str">
+        <x:v>Gladiator</x:v>
+      </x:c>
+      <x:c r="C42" s="66" t="str">
+        <x:v>Champion of the Arena</x:v>
+      </x:c>
+      <x:c r="D42" s="66" t="str">
+        <x:v>Iron gates rise and the crowd roars for blood. Maximus enters the sand beside you as Tigris of Gaul advances behind heavy armor.</x:v>
+      </x:c>
+      <x:c r="E42" s="66" t="str">
+        <x:v>Maximus</x:v>
+      </x:c>
+      <x:c r="F42" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G42" s="66" t="str">
+        <x:v>Tigris of Gaul</x:v>
+      </x:c>
+      <x:c r="H42" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I42" s="73" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J42" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K42" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L42" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M42" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N42" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O42" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P42" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q42" s="73" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="R42" s="73" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="S42" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T42" s="66" t="str">
+        <x:v>Arena minion Scene against the celebrated champion.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="48" customHeight="1">
+      <x:c r="A43" s="66" t="str">
+        <x:v>THING_GENERATOR_SHED</x:v>
+      </x:c>
+      <x:c r="B43" s="66" t="str">
+        <x:v>The Thing</x:v>
+      </x:c>
+      <x:c r="C43" s="66" t="str">
+        <x:v>Something in the Generator Shed</x:v>
+      </x:c>
+      <x:c r="D43" s="66" t="str">
+        <x:v>The outpost lights die one building at a time. MacReady raises his shotgun as an Infected Crewman backs toward the generator shed with an unfamiliar smile.</x:v>
+      </x:c>
+      <x:c r="E43" s="66" t="str">
+        <x:v>MacReady</x:v>
+      </x:c>
+      <x:c r="F43" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G43" s="66" t="str">
+        <x:v>Infected Crewman</x:v>
+      </x:c>
+      <x:c r="H43" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I43" s="73" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J43" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K43" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L43" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M43" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N43" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O43" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P43" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q43" s="73" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="R43" s="73" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="S43" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T43" s="66" t="str">
+        <x:v>Suspicion-driven minion Scene outside Outpost 31.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="48" customHeight="1">
+      <x:c r="A44" s="66" t="str">
+        <x:v>EMPIRE_ECHO_CORRIDOR</x:v>
+      </x:c>
+      <x:c r="B44" s="66" t="str">
+        <x:v>Star Wars: The Empire Strikes Back</x:v>
+      </x:c>
+      <x:c r="C44" s="66" t="str">
+        <x:v>Escape from Echo Base</x:v>
+      </x:c>
+      <x:c r="D44" s="66" t="str">
+        <x:v>Ice dust falls from the ceiling as warning sirens echo through the rebel base. Luke Skywalker reaches the hangar route while an Imperial Stormtrooper squad leader blocks the corridor.</x:v>
+      </x:c>
+      <x:c r="E44" s="66" t="str">
+        <x:v>Luke Skywalker</x:v>
+      </x:c>
+      <x:c r="F44" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G44" s="66" t="str">
+        <x:v>Imperial Stormtrooper</x:v>
+      </x:c>
+      <x:c r="H44" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I44" s="73" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J44" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K44" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L44" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M44" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N44" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O44" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P44" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q44" s="73" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="R44" s="73" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="S44" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T44" s="66" t="str">
+        <x:v>Echo Base evacuation minion Scene.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="48" customHeight="1">
+      <x:c r="A45" s="66" t="str">
+        <x:v>FLASHGORDON_SKY_CITY</x:v>
+      </x:c>
+      <x:c r="B45" s="66" t="str">
+        <x:v>Flash Gordon</x:v>
+      </x:c>
+      <x:c r="C45" s="66" t="str">
+        <x:v>Revolt Above the Clouds</x:v>
+      </x:c>
+      <x:c r="D45" s="66" t="str">
+        <x:v>Floating platforms buckle beneath an imperial bombardment. Flash Gordon reaches the landing bridge while a Hawkman champion challenges anyone attempting to cross.</x:v>
+      </x:c>
+      <x:c r="E45" s="66" t="str">
+        <x:v>Flash Gordon</x:v>
+      </x:c>
+      <x:c r="F45" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G45" s="66" t="str">
+        <x:v>Hawkman</x:v>
+      </x:c>
+      <x:c r="H45" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I45" s="73" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J45" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K45" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L45" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M45" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N45" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O45" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P45" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q45" s="73" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="R45" s="73" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="S45" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T45" s="66" t="str">
+        <x:v>Aerial minion challenge over Sky City.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="48" customHeight="1">
+      <x:c r="A46" s="66" t="str">
+        <x:v>WILLOW_NOCKMAAR_GATE</x:v>
+      </x:c>
+      <x:c r="B46" s="66" t="str">
+        <x:v>Willow</x:v>
+      </x:c>
+      <x:c r="C46" s="66" t="str">
+        <x:v>The Gate of Nockmaar</x:v>
+      </x:c>
+      <x:c r="D46" s="66" t="str">
+        <x:v>Rain runs black over the fortress stones as chains rattle above the moat. Willow Ufgood reaches the gate controls while a Nockmaar Soldier descends the stair with sword raised.</x:v>
+      </x:c>
+      <x:c r="E46" s="66" t="str">
+        <x:v>Willow Ufgood</x:v>
+      </x:c>
+      <x:c r="F46" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G46" s="66" t="str">
+        <x:v>Nockmaar Soldier</x:v>
+      </x:c>
+      <x:c r="H46" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I46" s="73" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J46" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K46" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L46" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M46" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N46" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O46" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P46" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q46" s="73" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="R46" s="73" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="S46" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T46" s="66" t="str">
+        <x:v>Fortress infiltration minion Scene.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="48" customHeight="1">
+      <x:c r="A47" s="66" t="str">
+        <x:v>LABYRINTH_GOBLIN_PATROL</x:v>
+      </x:c>
+      <x:c r="B47" s="66" t="str">
+        <x:v>Labyrinth</x:v>
+      </x:c>
+      <x:c r="C47" s="66" t="str">
+        <x:v>The Door That Wasn't There</x:v>
+      </x:c>
+      <x:c r="D47" s="66" t="str">
+        <x:v>A blank wall opens onto a corridor crowded with mismatched doors. Sarah Williams chooses a path while a Goblin Guard drags a club around the nearest corner.</x:v>
+      </x:c>
+      <x:c r="E47" s="66" t="str">
+        <x:v>Sarah Williams</x:v>
+      </x:c>
+      <x:c r="F47" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G47" s="66" t="str">
+        <x:v>Goblin Guard</x:v>
+      </x:c>
+      <x:c r="H47" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I47" s="73" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J47" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K47" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L47" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M47" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N47" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O47" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P47" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q47" s="73" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="R47" s="73" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="S47" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T47" s="66" t="str">
+        <x:v>Maze-navigation minion Scene.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="48" customHeight="1">
+      <x:c r="A48" s="66" t="str">
+        <x:v>TRON_DISC_ARENA</x:v>
+      </x:c>
+      <x:c r="B48" s="66" t="str">
+        <x:v>Tron</x:v>
+      </x:c>
+      <x:c r="C48" s="66" t="str">
+        <x:v>The Disc Arena</x:v>
+      </x:c>
+      <x:c r="D48" s="66" t="str">
+        <x:v>A glowing grid forms beneath the prisoners as walls rise around the arena. Kevin Flynn catches an identity disc while Sark steps onto the opposite platform.</x:v>
+      </x:c>
+      <x:c r="E48" s="66" t="str">
+        <x:v>Kevin Flynn</x:v>
+      </x:c>
+      <x:c r="F48" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G48" s="66" t="str">
+        <x:v>Sark</x:v>
+      </x:c>
+      <x:c r="H48" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I48" s="73" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J48" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K48" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L48" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M48" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N48" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O48" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P48" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q48" s="73" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="R48" s="73" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="S48" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T48" s="66" t="str">
+        <x:v>Digital arena minion Scene.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="48" customHeight="1">
+      <x:c r="A49" s="66" t="str">
+        <x:v>ARMYDARKNESS_GRAVEYARD</x:v>
+      </x:c>
+      <x:c r="B49" s="66" t="str">
+        <x:v>Army of Darkness</x:v>
+      </x:c>
+      <x:c r="C49" s="66" t="str">
+        <x:v>The Graveyard Awakens</x:v>
+      </x:c>
+      <x:c r="D49" s="66" t="str">
+        <x:v>Moonlight cuts across crooked stones as skeletal hands break through the soil. Ash Williams raises his boomstick while a Deadite Warrior claws free beside the open grave.</x:v>
+      </x:c>
+      <x:c r="E49" s="66" t="str">
+        <x:v>Ash Williams</x:v>
+      </x:c>
+      <x:c r="F49" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G49" s="66" t="str">
+        <x:v>Deadite Warrior</x:v>
+      </x:c>
+      <x:c r="H49" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I49" s="73" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J49" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K49" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L49" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M49" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N49" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O49" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P49" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q49" s="73" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="R49" s="73" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="S49" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T49" s="66" t="str">
+        <x:v>Graveyard minion Scene with improvised slapstick hazards.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="48" customHeight="1">
+      <x:c r="A50" s="66" t="str">
+        <x:v>STARGATE_TEMPLE_GATE</x:v>
+      </x:c>
+      <x:c r="B50" s="66" t="str">
+        <x:v>Stargate</x:v>
+      </x:c>
+      <x:c r="C50" s="66" t="str">
+        <x:v>The Horus Gate</x:v>
+      </x:c>
+      <x:c r="D50" s="66" t="str">
+        <x:v>Sunlight cuts through the temple doorway as villagers scatter across the courtyard. Daniel Jackson reaches the symbol wall while a Horus Guard lowers its staff weapon.</x:v>
+      </x:c>
+      <x:c r="E50" s="66" t="str">
+        <x:v>Daniel Jackson</x:v>
+      </x:c>
+      <x:c r="F50" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G50" s="66" t="str">
+        <x:v>Horus Guard</x:v>
+      </x:c>
+      <x:c r="H50" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I50" s="73" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J50" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K50" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L50" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M50" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N50" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O50" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P50" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q50" s="73" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="R50" s="73" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="S50" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T50" s="66" t="str">
+        <x:v>Temple uprising minion Scene.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="48" customHeight="1">
+      <x:c r="A51" s="66" t="str">
+        <x:v>EXCALIBUR_BLACK_BRIDGE</x:v>
+      </x:c>
+      <x:c r="B51" s="66" t="str">
+        <x:v>Excalibur</x:v>
+      </x:c>
+      <x:c r="C51" s="66" t="str">
+        <x:v>The Black Bridge</x:v>
+      </x:c>
+      <x:c r="D51" s="66" t="str">
+        <x:v>Mist covers a narrow bridge where shields and broken lances lie abandoned. King Arthur approaches beside you as the Black Knight lowers a lance and seals the crossing.</x:v>
+      </x:c>
+      <x:c r="E51" s="66" t="str">
+        <x:v>King Arthur</x:v>
+      </x:c>
+      <x:c r="F51" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G51" s="66" t="str">
+        <x:v>Black Knight</x:v>
+      </x:c>
+      <x:c r="H51" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I51" s="73" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J51" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K51" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L51" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M51" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N51" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O51" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P51" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q51" s="73" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="R51" s="73" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="S51" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T51" s="66" t="str">
+        <x:v>Chivalric minion duel at a guarded crossing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="48" customHeight="1">
+      <x:c r="A52" s="66" t="str">
+        <x:v>DUNE_SARDAUKAR_RAID</x:v>
+      </x:c>
+      <x:c r="B52" s="66" t="str">
+        <x:v>Dune 2021</x:v>
+      </x:c>
+      <x:c r="C52" s="66" t="str">
+        <x:v>Raid Beneath the Sand</x:v>
+      </x:c>
+      <x:c r="D52" s="66" t="str">
+        <x:v>Ornithopter wreckage burns beneath a moonless sky as blades move through the dust. Paul Atreides draws his crysknife while a Sardaukar Trooper descends the dune.</x:v>
+      </x:c>
+      <x:c r="E52" s="66" t="str">
+        <x:v>Paul Atreides</x:v>
+      </x:c>
+      <x:c r="F52" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G52" s="66" t="str">
+        <x:v>Sardaukar Trooper</x:v>
+      </x:c>
+      <x:c r="H52" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I52" s="73" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J52" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K52" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L52" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M52" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N52" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O52" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P52" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q52" s="73" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="R52" s="73" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="S52" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T52" s="66" t="str">
+        <x:v>Desert minion ambush against an elite trooper.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fb6d1e548214eb7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25057a83c0c04cad"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16958,10 +18012,4260 @@
         <x:v>Perception is favored.</x:v>
       </x:c>
     </x:row>
+    <x:row r="172" ht="48" customHeight="1">
+      <x:c r="A172" s="66" t="str">
+        <x:v>TOTALRECALL_REKALL_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B172" s="66" t="str">
+        <x:v>BREAK_SHUTTER</x:v>
+      </x:c>
+      <x:c r="C172" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D172" s="66" t="str">
+        <x:v>Force a security shutter open before Richter reaches the corridor.</x:v>
+      </x:c>
+      <x:c r="E172" s="73" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F172" s="66" t="str">
+        <x:v>The shutter buckles and Quaid pulls you into the service hall.</x:v>
+      </x:c>
+      <x:c r="G172" s="66" t="str">
+        <x:v>The mechanism locks and Richter corners you at the controls.</x:v>
+      </x:c>
+      <x:c r="H172" s="73" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I172" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J172" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K172" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L172" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M172" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N172" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O172" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P172" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="48" customHeight="1">
+      <x:c r="A173" s="66" t="str">
+        <x:v>TOTALRECALL_REKALL_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B173" s="66" t="str">
+        <x:v>IGNORE_IMPLANT</x:v>
+      </x:c>
+      <x:c r="C173" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D173" s="66" t="str">
+        <x:v>Fight through the memory procedure's aftereffects and keep moving.</x:v>
+      </x:c>
+      <x:c r="E173" s="73" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F173" s="66" t="str">
+        <x:v>You steady yourself and guide Quaid through the distorted clinic.</x:v>
+      </x:c>
+      <x:c r="G173" s="66" t="str">
+        <x:v>A false memory freezes you long enough for Richter to arrive.</x:v>
+      </x:c>
+      <x:c r="H173" s="73" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I173" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J173" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K173" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L173" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M173" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N173" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O173" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P173" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="48" customHeight="1">
+      <x:c r="A174" s="66" t="str">
+        <x:v>TOTALRECALL_REKALL_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B174" s="66" t="str">
+        <x:v>SLIDE_LAB</x:v>
+      </x:c>
+      <x:c r="C174" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D174" s="66" t="str">
+        <x:v>Slide across the procedure table and enter the ventilation passage.</x:v>
+      </x:c>
+      <x:c r="E174" s="73" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F174" s="66" t="str">
+        <x:v>You clear the lab and flank Richter through the adjoining room.</x:v>
+      </x:c>
+      <x:c r="G174" s="66" t="str">
+        <x:v>Loose instruments scatter across the floor and betray the route.</x:v>
+      </x:c>
+      <x:c r="H174" s="73" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="I174" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J174" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K174" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L174" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M174" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N174" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O174" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P174" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="48" customHeight="1">
+      <x:c r="A175" s="66" t="str">
+        <x:v>TOTALRECALL_REKALL_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B175" s="66" t="str">
+        <x:v>TRUST_MEMORY</x:v>
+      </x:c>
+      <x:c r="C175" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D175" s="66" t="str">
+        <x:v>Follow a half-remembered escape route that may never have existed.</x:v>
+      </x:c>
+      <x:c r="E175" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F175" s="66" t="str">
+        <x:v>The imagined corridor proves real and opens behind Richter.</x:v>
+      </x:c>
+      <x:c r="G175" s="66" t="str">
+        <x:v>The memory ends at a blank wall as Richter enters.</x:v>
+      </x:c>
+      <x:c r="H175" s="73" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I175" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J175" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K175" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L175" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M175" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N175" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O175" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P175" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="48" customHeight="1">
+      <x:c r="A176" s="66" t="str">
+        <x:v>TOTALRECALL_REKALL_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B176" s="66" t="str">
+        <x:v>READ_CAMERAS</x:v>
+      </x:c>
+      <x:c r="C176" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D176" s="66" t="str">
+        <x:v>Compare clinic cameras to identify which image of Richter is current.</x:v>
+      </x:c>
+      <x:c r="E176" s="73" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F176" s="66" t="str">
+        <x:v>A timestamp exposes his true position and lets Quaid prepare.</x:v>
+      </x:c>
+      <x:c r="G176" s="66" t="str">
+        <x:v>A looping recording sends you toward his approach.</x:v>
+      </x:c>
+      <x:c r="H176" s="73" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I176" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J176" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K176" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L176" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M176" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N176" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O176" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P176" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="48" customHeight="1">
+      <x:c r="A177" s="66" t="str">
+        <x:v>STARTREKVI_CONSPIRACY</x:v>
+      </x:c>
+      <x:c r="B177" s="66" t="str">
+        <x:v>JAM_LIFT</x:v>
+      </x:c>
+      <x:c r="C177" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D177" s="66" t="str">
+        <x:v>Force the turbolift doors closed before Valeris clears them.</x:v>
+      </x:c>
+      <x:c r="E177" s="73" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F177" s="66" t="str">
+        <x:v>The doors lock and deny her prepared firing lane.</x:v>
+      </x:c>
+      <x:c r="G177" s="66" t="str">
+        <x:v>The doors reopen under emergency power and expose you.</x:v>
+      </x:c>
+      <x:c r="H177" s="73" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I177" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J177" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K177" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L177" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M177" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N177" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O177" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P177" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="48" customHeight="1">
+      <x:c r="A178" s="66" t="str">
+        <x:v>STARTREKVI_CONSPIRACY</x:v>
+      </x:c>
+      <x:c r="B178" s="66" t="str">
+        <x:v>CROSS_STUN_FIRE</x:v>
+      </x:c>
+      <x:c r="C178" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D178" s="66" t="str">
+        <x:v>Advance through suppressing fire while Kirk reaches the terminal.</x:v>
+      </x:c>
+      <x:c r="E178" s="73" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F178" s="66" t="str">
+        <x:v>You endure the barrage and keep Valeris occupied.</x:v>
+      </x:c>
+      <x:c r="G178" s="66" t="str">
+        <x:v>A near strike breaks your advance and she closes in.</x:v>
+      </x:c>
+      <x:c r="H178" s="73" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I178" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J178" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K178" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L178" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M178" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N178" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O178" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P178" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="48" customHeight="1">
+      <x:c r="A179" s="66" t="str">
+        <x:v>STARTREKVI_CONSPIRACY</x:v>
+      </x:c>
+      <x:c r="B179" s="66" t="str">
+        <x:v>JEFFERIES_TUBE</x:v>
+      </x:c>
+      <x:c r="C179" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D179" s="66" t="str">
+        <x:v>Enter the narrow maintenance tube and circle behind Valeris.</x:v>
+      </x:c>
+      <x:c r="E179" s="73" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F179" s="66" t="str">
+        <x:v>You emerge at the junction behind her position.</x:v>
+      </x:c>
+      <x:c r="G179" s="66" t="str">
+        <x:v>A loose access panel announces your movement.</x:v>
+      </x:c>
+      <x:c r="H179" s="73" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="I179" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J179" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K179" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L179" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M179" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N179" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O179" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P179" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="48" customHeight="1">
+      <x:c r="A180" s="66" t="str">
+        <x:v>STARTREKVI_CONSPIRACY</x:v>
+      </x:c>
+      <x:c r="B180" s="66" t="str">
+        <x:v>ISSUE_FALSE_ORDER</x:v>
+      </x:c>
+      <x:c r="C180" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D180" s="66" t="str">
+        <x:v>Transmit a false command and gamble that Valeris obeys protocol.</x:v>
+      </x:c>
+      <x:c r="E180" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F180" s="66" t="str">
+        <x:v>She hesitates long enough for Kirk to expose the conspiracy.</x:v>
+      </x:c>
+      <x:c r="G180" s="66" t="str">
+        <x:v>She recognizes the forged authorization immediately.</x:v>
+      </x:c>
+      <x:c r="H180" s="73" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I180" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J180" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K180" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L180" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M180" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N180" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O180" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P180" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="48" customHeight="1">
+      <x:c r="A181" s="66" t="str">
+        <x:v>STARTREKVI_CONSPIRACY</x:v>
+      </x:c>
+      <x:c r="B181" s="66" t="str">
+        <x:v>CHECK_LOGIC</x:v>
+      </x:c>
+      <x:c r="C181" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D181" s="66" t="str">
+        <x:v>Find the contradiction hidden inside Valeris's carefully logical account.</x:v>
+      </x:c>
+      <x:c r="E181" s="73" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F181" s="66" t="str">
+        <x:v>The inconsistency reveals where she concealed the evidence.</x:v>
+      </x:c>
+      <x:c r="G181" s="66" t="str">
+        <x:v>A planted detail leads you into her prepared ambush.</x:v>
+      </x:c>
+      <x:c r="H181" s="73" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I181" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J181" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K181" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L181" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M181" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N181" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O181" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P181" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="48" customHeight="1">
+      <x:c r="A182" s="66" t="str">
+        <x:v>THREEHUNDRED_IMMORTAL_NIGHT</x:v>
+      </x:c>
+      <x:c r="B182" s="66" t="str">
+        <x:v>RAISE_WALL</x:v>
+      </x:c>
+      <x:c r="C182" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D182" s="66" t="str">
+        <x:v>Lift a fallen shield into the breach beside Leonidas.</x:v>
+      </x:c>
+      <x:c r="E182" s="73" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F182" s="66" t="str">
+        <x:v>The shield wall reforms and traps the Immortal in the pass.</x:v>
+      </x:c>
+      <x:c r="G182" s="66" t="str">
+        <x:v>The shield slips and the Immortal attacks through the gap.</x:v>
+      </x:c>
+      <x:c r="H182" s="73" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="I182" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J182" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K182" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L182" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M182" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N182" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O182" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P182" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="48" customHeight="1">
+      <x:c r="A183" s="66" t="str">
+        <x:v>THREEHUNDRED_IMMORTAL_NIGHT</x:v>
+      </x:c>
+      <x:c r="B183" s="66" t="str">
+        <x:v>HOLD_SPEAR</x:v>
+      </x:c>
+      <x:c r="C183" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D183" s="66" t="str">
+        <x:v>Hold the extended spear line while the Immortal tests it.</x:v>
+      </x:c>
+      <x:c r="E183" s="73" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F183" s="66" t="str">
+        <x:v>You withstand the pressure until Leonidas finds an opening.</x:v>
+      </x:c>
+      <x:c r="G183" s="66" t="str">
+        <x:v>Your arms fail and the spear line folds inward.</x:v>
+      </x:c>
+      <x:c r="H183" s="73" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I183" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J183" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K183" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L183" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M183" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N183" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O183" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P183" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" ht="48" customHeight="1">
+      <x:c r="A184" s="66" t="str">
+        <x:v>THREEHUNDRED_IMMORTAL_NIGHT</x:v>
+      </x:c>
+      <x:c r="B184" s="66" t="str">
+        <x:v>VAULT_SHIELDS</x:v>
+      </x:c>
+      <x:c r="C184" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D184" s="66" t="str">
+        <x:v>Vault the shield wall and land beyond the Immortal's guard.</x:v>
+      </x:c>
+      <x:c r="E184" s="73" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F184" s="66" t="str">
+        <x:v>You land cleanly and turn the masked warrior toward Leonidas.</x:v>
+      </x:c>
+      <x:c r="G184" s="66" t="str">
+        <x:v>The warrior reads the leap and meets you in the air.</x:v>
+      </x:c>
+      <x:c r="H184" s="73" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I184" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J184" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K184" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L184" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M184" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N184" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O184" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P184" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="48" customHeight="1">
+      <x:c r="A185" s="66" t="str">
+        <x:v>THREEHUNDRED_IMMORTAL_NIGHT</x:v>
+      </x:c>
+      <x:c r="B185" s="66" t="str">
+        <x:v>THROW_IN_DARK</x:v>
+      </x:c>
+      <x:c r="C185" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D185" s="66" t="str">
+        <x:v>Cast a spear toward the sound of breathing in the dark.</x:v>
+      </x:c>
+      <x:c r="E185" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F185" s="66" t="str">
+        <x:v>The throw tears away the Immortal's mask and ruins the ambush.</x:v>
+      </x:c>
+      <x:c r="G185" s="66" t="str">
+        <x:v>The spear strikes only stone and reveals your position.</x:v>
+      </x:c>
+      <x:c r="H185" s="73" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I185" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J185" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K185" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L185" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M185" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N185" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O185" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P185" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" ht="48" customHeight="1">
+      <x:c r="A186" s="66" t="str">
+        <x:v>THREEHUNDRED_IMMORTAL_NIGHT</x:v>
+      </x:c>
+      <x:c r="B186" s="66" t="str">
+        <x:v>WATCH_DUST</x:v>
+      </x:c>
+      <x:c r="C186" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D186" s="66" t="str">
+        <x:v>Follow disturbed dust beneath the Immortal's silent steps.</x:v>
+      </x:c>
+      <x:c r="E186" s="73" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F186" s="66" t="str">
+        <x:v>The dust reveals the attack a heartbeat before it begins.</x:v>
+      </x:c>
+      <x:c r="G186" s="66" t="str">
+        <x:v>Wind across the pass creates a false trail.</x:v>
+      </x:c>
+      <x:c r="H186" s="73" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I186" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J186" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K186" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L186" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M186" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N186" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O186" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P186" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="48" customHeight="1">
+      <x:c r="A187" s="66" t="str">
+        <x:v>T2_FREEWAY_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B187" s="66" t="str">
+        <x:v>TIP_TRUCK</x:v>
+      </x:c>
+      <x:c r="C187" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D187" s="66" t="str">
+        <x:v>Tip a damaged truck frame into the endoskeleton's route.</x:v>
+      </x:c>
+      <x:c r="E187" s="73" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F187" s="66" t="str">
+        <x:v>The wreck pins one metal leg and gives Sarah a clear shot.</x:v>
+      </x:c>
+      <x:c r="G187" s="66" t="str">
+        <x:v>The frame collapses short of the target.</x:v>
+      </x:c>
+      <x:c r="H187" s="73" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="I187" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J187" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K187" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L187" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M187" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N187" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O187" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P187" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" ht="48" customHeight="1">
+      <x:c r="A188" s="66" t="str">
+        <x:v>T2_FREEWAY_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B188" s="66" t="str">
+        <x:v>CROSS_FIRE</x:v>
+      </x:c>
+      <x:c r="C188" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D188" s="66" t="str">
+        <x:v>Draw the machine's fire while Sarah moves between vehicles.</x:v>
+      </x:c>
+      <x:c r="E188" s="73" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F188" s="66" t="str">
+        <x:v>You endure the barrage and hold its targeting focus.</x:v>
+      </x:c>
+      <x:c r="G188" s="66" t="str">
+        <x:v>The sustained fire forces you out of cover.</x:v>
+      </x:c>
+      <x:c r="H188" s="73" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I188" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J188" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K188" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L188" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M188" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N188" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O188" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P188" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" ht="48" customHeight="1">
+      <x:c r="A189" s="66" t="str">
+        <x:v>T2_FREEWAY_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B189" s="66" t="str">
+        <x:v>UNDER_WRECK</x:v>
+      </x:c>
+      <x:c r="C189" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D189" s="66" t="str">
+        <x:v>Crawl beneath the wreckage and attack its exposed rear assembly.</x:v>
+      </x:c>
+      <x:c r="E189" s="73" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F189" s="66" t="str">
+        <x:v>You emerge behind the machine before it recalibrates.</x:v>
+      </x:c>
+      <x:c r="G189" s="66" t="str">
+        <x:v>A hanging axle catches your gear and alerts it.</x:v>
+      </x:c>
+      <x:c r="H189" s="73" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I189" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J189" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K189" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L189" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M189" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N189" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O189" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P189" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="48" customHeight="1">
+      <x:c r="A190" s="66" t="str">
+        <x:v>T2_FREEWAY_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B190" s="66" t="str">
+        <x:v>START_ENGINE</x:v>
+      </x:c>
+      <x:c r="C190" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D190" s="66" t="str">
+        <x:v>Turn the key in a ruined vehicle and gamble that it still runs.</x:v>
+      </x:c>
+      <x:c r="E190" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F190" s="66" t="str">
+        <x:v>The engine surges forward and smashes into the endoskeleton.</x:v>
+      </x:c>
+      <x:c r="G190" s="66" t="str">
+        <x:v>The starter clicks uselessly in the silence.</x:v>
+      </x:c>
+      <x:c r="H190" s="73" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I190" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J190" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K190" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L190" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M190" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N190" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O190" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P190" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" ht="48" customHeight="1">
+      <x:c r="A191" s="66" t="str">
+        <x:v>T2_FREEWAY_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B191" s="66" t="str">
+        <x:v>TRACK_OPTICS</x:v>
+      </x:c>
+      <x:c r="C191" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D191" s="66" t="str">
+        <x:v>Watch the red optic and predict its next targeting sweep.</x:v>
+      </x:c>
+      <x:c r="E191" s="73" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F191" s="66" t="str">
+        <x:v>You call the sweep and Sarah fires between scans.</x:v>
+      </x:c>
+      <x:c r="G191" s="66" t="str">
+        <x:v>Smoke reflects the optic and hides its true aim.</x:v>
+      </x:c>
+      <x:c r="H191" s="73" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I191" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J191" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K191" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L191" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M191" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N191" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O191" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P191" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" ht="48" customHeight="1">
+      <x:c r="A192" s="66" t="str">
+        <x:v>TWOTOWERS_DEEPING_BREACH</x:v>
+      </x:c>
+      <x:c r="B192" s="66" t="str">
+        <x:v>PUSH_LADDER</x:v>
+      </x:c>
+      <x:c r="C192" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D192" s="66" t="str">
+        <x:v>Push the siege ladder away before more Uruk-hai reach the wall.</x:v>
+      </x:c>
+      <x:c r="E192" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F192" s="66" t="str">
+        <x:v>The ladder falls and isolates the Berserker beside Aragorn.</x:v>
+      </x:c>
+      <x:c r="G192" s="66" t="str">
+        <x:v>The ladder's hooks hold and the Berserker clears the parapet.</x:v>
+      </x:c>
+      <x:c r="H192" s="73" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I192" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J192" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K192" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L192" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M192" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N192" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O192" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P192" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" ht="48" customHeight="1">
+      <x:c r="A193" s="66" t="str">
+        <x:v>TWOTOWERS_DEEPING_BREACH</x:v>
+      </x:c>
+      <x:c r="B193" s="66" t="str">
+        <x:v>HOLD_BREACH</x:v>
+      </x:c>
+      <x:c r="C193" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D193" s="66" t="str">
+        <x:v>Stand in the broken wall while Aragorn rallies the defenders.</x:v>
+      </x:c>
+      <x:c r="E193" s="73" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F193" s="66" t="str">
+        <x:v>You hold the narrow breach and absorb the first assault.</x:v>
+      </x:c>
+      <x:c r="G193" s="66" t="str">
+        <x:v>The Berserker drives you back into the courtyard.</x:v>
+      </x:c>
+      <x:c r="H193" s="73" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="I193" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J193" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K193" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L193" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M193" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N193" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O193" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P193" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" ht="48" customHeight="1">
+      <x:c r="A194" s="66" t="str">
+        <x:v>TWOTOWERS_DEEPING_BREACH</x:v>
+      </x:c>
+      <x:c r="B194" s="66" t="str">
+        <x:v>CROSS_PARAPET</x:v>
+      </x:c>
+      <x:c r="C194" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D194" s="66" t="str">
+        <x:v>Run the rain-slick parapet and strike from the tower side.</x:v>
+      </x:c>
+      <x:c r="E194" s="73" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F194" s="66" t="str">
+        <x:v>You reach the flank before the Berserker turns.</x:v>
+      </x:c>
+      <x:c r="G194" s="66" t="str">
+        <x:v>Your footing slips on the broken stone.</x:v>
+      </x:c>
+      <x:c r="H194" s="73" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I194" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J194" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K194" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L194" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M194" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N194" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O194" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P194" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" ht="48" customHeight="1">
+      <x:c r="A195" s="66" t="str">
+        <x:v>TWOTOWERS_DEEPING_BREACH</x:v>
+      </x:c>
+      <x:c r="B195" s="66" t="str">
+        <x:v>CUT_ROPE</x:v>
+      </x:c>
+      <x:c r="C195" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D195" s="66" t="str">
+        <x:v>Cut one siege rope and gamble on which ladder it supports.</x:v>
+      </x:c>
+      <x:c r="E195" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F195" s="66" t="str">
+        <x:v>The correct ladder twists away and exposes the Berserker.</x:v>
+      </x:c>
+      <x:c r="G195" s="66" t="str">
+        <x:v>The rope belongs to a defender's barricade.</x:v>
+      </x:c>
+      <x:c r="H195" s="73" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I195" s="73" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J195" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K195" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L195" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M195" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N195" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O195" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P195" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" ht="48" customHeight="1">
+      <x:c r="A196" s="66" t="str">
+        <x:v>TWOTOWERS_DEEPING_BREACH</x:v>
+      </x:c>
+      <x:c r="B196" s="66" t="str">
+        <x:v>SPOT_CHARGE</x:v>
+      </x:c>
+      <x:c r="C196" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D196" s="66" t="str">
+        <x:v>Identify the Berserker carrying the explosive charge through the rain.</x:v>
+      </x:c>
+      <x:c r="E196" s="73" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F196" s="66" t="str">
+        <x:v>You point out the threat and Aragorn intercepts it.</x:v>
+      </x:c>
+      <x:c r="G196" s="66" t="str">
+        <x:v>A decoy charge draws your warning away.</x:v>
+      </x:c>
+      <x:c r="H196" s="73" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I196" s="73" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J196" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K196" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L196" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M196" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N196" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O196" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P196" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" ht="48" customHeight="1">
+      <x:c r="A197" s="66" t="str">
+        <x:v>MATRIX_ROOFTOP_AGENT</x:v>
+      </x:c>
+      <x:c r="B197" s="66" t="str">
+        <x:v>BEND_MAST</x:v>
+      </x:c>
+      <x:c r="C197" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D197" s="66" t="str">
+        <x:v>Pull down the antenna mast across Jones's firing position.</x:v>
+      </x:c>
+      <x:c r="E197" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F197" s="66" t="str">
+        <x:v>The mast forces the Agent into Neo's line of attack.</x:v>
+      </x:c>
+      <x:c r="G197" s="66" t="str">
+        <x:v>Jones catches the falling structure and turns it aside.</x:v>
+      </x:c>
+      <x:c r="H197" s="73" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I197" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J197" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K197" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L197" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M197" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N197" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O197" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P197" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="48" customHeight="1">
+      <x:c r="A198" s="66" t="str">
+        <x:v>MATRIX_ROOFTOP_AGENT</x:v>
+      </x:c>
+      <x:c r="B198" s="66" t="str">
+        <x:v>IGNORE_BULLETS</x:v>
+      </x:c>
+      <x:c r="C198" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D198" s="66" t="str">
+        <x:v>Keep moving despite the simulation's impact warnings.</x:v>
+      </x:c>
+      <x:c r="E198" s="73" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F198" s="66" t="str">
+        <x:v>You remain focused and hold Jones's attention.</x:v>
+      </x:c>
+      <x:c r="G198" s="66" t="str">
+        <x:v>The pain response overwhelms your concentration.</x:v>
+      </x:c>
+      <x:c r="H198" s="73" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="I198" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J198" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K198" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L198" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M198" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N198" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O198" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P198" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="48" customHeight="1">
+      <x:c r="A199" s="66" t="str">
+        <x:v>MATRIX_ROOFTOP_AGENT</x:v>
+      </x:c>
+      <x:c r="B199" s="66" t="str">
+        <x:v>ROOFTOP_LEAP</x:v>
+      </x:c>
+      <x:c r="C199" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D199" s="66" t="str">
+        <x:v>Leap the gap to the adjacent roof and attack from above.</x:v>
+      </x:c>
+      <x:c r="E199" s="73" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F199" s="66" t="str">
+        <x:v>You clear the gap and arrive beyond Jones's tracking arc.</x:v>
+      </x:c>
+      <x:c r="G199" s="66" t="str">
+        <x:v>The distance stretches as the Matrix resists you.</x:v>
+      </x:c>
+      <x:c r="H199" s="73" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I199" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J199" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K199" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L199" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M199" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N199" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O199" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P199" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" ht="48" customHeight="1">
+      <x:c r="A200" s="66" t="str">
+        <x:v>MATRIX_ROOFTOP_AGENT</x:v>
+      </x:c>
+      <x:c r="B200" s="66" t="str">
+        <x:v>ENTER_GLITCH</x:v>
+      </x:c>
+      <x:c r="C200" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D200" s="66" t="str">
+        <x:v>Step into a flickering service door before its destination stabilizes.</x:v>
+      </x:c>
+      <x:c r="E200" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F200" s="66" t="str">
+        <x:v>The glitch deposits you behind the Agent.</x:v>
+      </x:c>
+      <x:c r="G200" s="66" t="str">
+        <x:v>The door loops back into his sights.</x:v>
+      </x:c>
+      <x:c r="H200" s="73" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I200" s="73" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J200" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K200" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L200" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M200" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N200" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O200" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P200" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" ht="48" customHeight="1">
+      <x:c r="A201" s="66" t="str">
+        <x:v>MATRIX_ROOFTOP_AGENT</x:v>
+      </x:c>
+      <x:c r="B201" s="66" t="str">
+        <x:v>SEE_POSSESSION</x:v>
+      </x:c>
+      <x:c r="C201" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D201" s="66" t="str">
+        <x:v>Watch the crowd below for the next body Jones intends to occupy.</x:v>
+      </x:c>
+      <x:c r="E201" s="73" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F201" s="66" t="str">
+        <x:v>You identify the transfer before it completes.</x:v>
+      </x:c>
+      <x:c r="G201" s="66" t="str">
+        <x:v>A harmless bystander flickers and draws your attention.</x:v>
+      </x:c>
+      <x:c r="H201" s="73" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I201" s="73" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J201" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K201" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L201" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M201" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N201" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O201" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P201" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="48" customHeight="1">
+      <x:c r="A202" s="66" t="str">
+        <x:v>GLADIATOR_TIGRIS_ARENA</x:v>
+      </x:c>
+      <x:c r="B202" s="66" t="str">
+        <x:v>BREAK_CHAIN</x:v>
+      </x:c>
+      <x:c r="C202" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D202" s="66" t="str">
+        <x:v>Break the chain controlling the arena obstacle between you.</x:v>
+      </x:c>
+      <x:c r="E202" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F202" s="66" t="str">
+        <x:v>The obstacle falls and traps Tigris away from his support.</x:v>
+      </x:c>
+      <x:c r="G202" s="66" t="str">
+        <x:v>The chain snaps toward you and opens the fight.</x:v>
+      </x:c>
+      <x:c r="H202" s="73" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I202" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J202" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K202" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L202" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M202" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N202" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O202" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P202" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="48" customHeight="1">
+      <x:c r="A203" s="66" t="str">
+        <x:v>GLADIATOR_TIGRIS_ARENA</x:v>
+      </x:c>
+      <x:c r="B203" s="66" t="str">
+        <x:v>MEET_CHARGE</x:v>
+      </x:c>
+      <x:c r="C203" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D203" s="66" t="str">
+        <x:v>Meet Tigris's charge and hold the center for Maximus.</x:v>
+      </x:c>
+      <x:c r="E203" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F203" s="66" t="str">
+        <x:v>You withstand the impact and halt his momentum.</x:v>
+      </x:c>
+      <x:c r="G203" s="66" t="str">
+        <x:v>The armored charge drives you through the sand.</x:v>
+      </x:c>
+      <x:c r="H203" s="73" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I203" s="73" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J203" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K203" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L203" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M203" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N203" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O203" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P203" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="48" customHeight="1">
+      <x:c r="A204" s="66" t="str">
+        <x:v>GLADIATOR_TIGRIS_ARENA</x:v>
+      </x:c>
+      <x:c r="B204" s="66" t="str">
+        <x:v>ROLL_BLADE</x:v>
+      </x:c>
+      <x:c r="C204" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D204" s="66" t="str">
+        <x:v>Roll beneath the war sword and reach Tigris's unarmored side.</x:v>
+      </x:c>
+      <x:c r="E204" s="73" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F204" s="66" t="str">
+        <x:v>You clear the blade and force him to turn.</x:v>
+      </x:c>
+      <x:c r="G204" s="66" t="str">
+        <x:v>The sword changes direction inside the swing.</x:v>
+      </x:c>
+      <x:c r="H204" s="73" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="I204" s="73" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J204" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K204" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L204" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M204" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N204" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O204" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P204" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="48" customHeight="1">
+      <x:c r="A205" s="66" t="str">
+        <x:v>GLADIATOR_TIGRIS_ARENA</x:v>
+      </x:c>
+      <x:c r="B205" s="66" t="str">
+        <x:v>RELEASE_GATE</x:v>
+      </x:c>
+      <x:c r="C205" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D205" s="66" t="str">
+        <x:v>Pull an unmarked arena lever and gamble on what it releases.</x:v>
+      </x:c>
+      <x:c r="E205" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F205" s="66" t="str">
+        <x:v>A gate rises behind Tigris and blocks his retreat.</x:v>
+      </x:c>
+      <x:c r="G205" s="66" t="str">
+        <x:v>The lever opens another hazard beside you.</x:v>
+      </x:c>
+      <x:c r="H205" s="73" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I205" s="73" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J205" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K205" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L205" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M205" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N205" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O205" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P205" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="48" customHeight="1">
+      <x:c r="A206" s="66" t="str">
+        <x:v>GLADIATOR_TIGRIS_ARENA</x:v>
+      </x:c>
+      <x:c r="B206" s="66" t="str">
+        <x:v>READ_ARMOR</x:v>
+      </x:c>
+      <x:c r="C206" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D206" s="66" t="str">
+        <x:v>Study the dents in Tigris's armor for the joint he protects.</x:v>
+      </x:c>
+      <x:c r="E206" s="73" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F206" s="66" t="str">
+        <x:v>The wear reveals a weak shoulder fastening.</x:v>
+      </x:c>
+      <x:c r="G206" s="66" t="str">
+        <x:v>Decorative damage disguises the strongest plate.</x:v>
+      </x:c>
+      <x:c r="H206" s="73" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="I206" s="73" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J206" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K206" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L206" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M206" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N206" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O206" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P206" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="48" customHeight="1">
+      <x:c r="A207" s="66" t="str">
+        <x:v>THING_GENERATOR_SHED</x:v>
+      </x:c>
+      <x:c r="B207" s="66" t="str">
+        <x:v>BAR_DOOR</x:v>
+      </x:c>
+      <x:c r="C207" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D207" s="66" t="str">
+        <x:v>Jam a steel bar through the shed door before the imitation escapes.</x:v>
+      </x:c>
+      <x:c r="E207" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F207" s="66" t="str">
+        <x:v>The door holds and contains the creature with MacReady.</x:v>
+      </x:c>
+      <x:c r="G207" s="66" t="str">
+        <x:v>The frame tears apart under inhuman strength.</x:v>
+      </x:c>
+      <x:c r="H207" s="73" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I207" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J207" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K207" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L207" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M207" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N207" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O207" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P207" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" ht="48" customHeight="1">
+      <x:c r="A208" s="66" t="str">
+        <x:v>THING_GENERATOR_SHED</x:v>
+      </x:c>
+      <x:c r="B208" s="66" t="str">
+        <x:v>CROSS_BLIZZARD</x:v>
+      </x:c>
+      <x:c r="C208" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D208" s="66" t="str">
+        <x:v>Circle the shed through the blizzard without losing the trail.</x:v>
+      </x:c>
+      <x:c r="E208" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F208" s="66" t="str">
+        <x:v>You endure the cold and seal the rear exit.</x:v>
+      </x:c>
+      <x:c r="G208" s="66" t="str">
+        <x:v>The wind erases the tracks and slows you.</x:v>
+      </x:c>
+      <x:c r="H208" s="73" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I208" s="73" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J208" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K208" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L208" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M208" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N208" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O208" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P208" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" ht="48" customHeight="1">
+      <x:c r="A209" s="66" t="str">
+        <x:v>THING_GENERATOR_SHED</x:v>
+      </x:c>
+      <x:c r="B209" s="66" t="str">
+        <x:v>CLIMB_ROOF</x:v>
+      </x:c>
+      <x:c r="C209" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D209" s="66" t="str">
+        <x:v>Climb the iced roof and enter through the generator vent.</x:v>
+      </x:c>
+      <x:c r="E209" s="73" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F209" s="66" t="str">
+        <x:v>You reach the rafters above the imitation.</x:v>
+      </x:c>
+      <x:c r="G209" s="66" t="str">
+        <x:v>Ice breaks away and drops you beside it.</x:v>
+      </x:c>
+      <x:c r="H209" s="73" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="I209" s="73" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J209" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K209" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L209" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M209" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N209" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O209" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P209" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" ht="48" customHeight="1">
+      <x:c r="A210" s="66" t="str">
+        <x:v>THING_GENERATOR_SHED</x:v>
+      </x:c>
+      <x:c r="B210" s="66" t="str">
+        <x:v>CUT_FUEL</x:v>
+      </x:c>
+      <x:c r="C210" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D210" s="66" t="str">
+        <x:v>Cut one fuel hose and gamble that it feeds the generator rather than the heater.</x:v>
+      </x:c>
+      <x:c r="E210" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F210" s="66" t="str">
+        <x:v>The lights flare and expose the creature changing shape.</x:v>
+      </x:c>
+      <x:c r="G210" s="66" t="str">
+        <x:v>The outpost falls darker while the creature moves.</x:v>
+      </x:c>
+      <x:c r="H210" s="73" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I210" s="73" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J210" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K210" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L210" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M210" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N210" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O210" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P210" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="48" customHeight="1">
+      <x:c r="A211" s="66" t="str">
+        <x:v>THING_GENERATOR_SHED</x:v>
+      </x:c>
+      <x:c r="B211" s="66" t="str">
+        <x:v>CHECK_BREATH</x:v>
+      </x:c>
+      <x:c r="C211" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D211" s="66" t="str">
+        <x:v>Compare everyone's breath and movement in the freezing air.</x:v>
+      </x:c>
+      <x:c r="E211" s="73" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F211" s="66" t="str">
+        <x:v>One pattern remains wrong and reveals the infected crewman.</x:v>
+      </x:c>
+      <x:c r="G211" s="66" t="str">
+        <x:v>Fear makes an innocent crewman appear unnatural.</x:v>
+      </x:c>
+      <x:c r="H211" s="73" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="I211" s="73" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J211" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K211" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L211" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M211" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N211" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O211" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P211" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" ht="48" customHeight="1">
+      <x:c r="A212" s="66" t="str">
+        <x:v>EMPIRE_ECHO_CORRIDOR</x:v>
+      </x:c>
+      <x:c r="B212" s="66" t="str">
+        <x:v>MOVE_CANNON</x:v>
+      </x:c>
+      <x:c r="C212" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D212" s="66" t="str">
+        <x:v>Drag a disabled cannon across the stormtrooper's firing lane.</x:v>
+      </x:c>
+      <x:c r="E212" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F212" s="66" t="str">
+        <x:v>The cannon forms cover and lets Luke advance.</x:v>
+      </x:c>
+      <x:c r="G212" s="66" t="str">
+        <x:v>The frozen mount locks before reaching the lane.</x:v>
+      </x:c>
+      <x:c r="H212" s="73" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="I212" s="73" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J212" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K212" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L212" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M212" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N212" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O212" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P212" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" ht="48" customHeight="1">
+      <x:c r="A213" s="66" t="str">
+        <x:v>EMPIRE_ECHO_CORRIDOR</x:v>
+      </x:c>
+      <x:c r="B213" s="66" t="str">
+        <x:v>CROSS_BLASTER_FIRE</x:v>
+      </x:c>
+      <x:c r="C213" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D213" s="66" t="str">
+        <x:v>Draw blaster fire while evacuees clear the junction.</x:v>
+      </x:c>
+      <x:c r="E213" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F213" s="66" t="str">
+        <x:v>You hold the corridor until Luke reaches the squad.</x:v>
+      </x:c>
+      <x:c r="G213" s="66" t="str">
+        <x:v>The barrage forces you against the blast door.</x:v>
+      </x:c>
+      <x:c r="H213" s="73" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I213" s="73" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J213" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K213" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L213" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M213" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N213" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O213" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P213" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" ht="48" customHeight="1">
+      <x:c r="A214" s="66" t="str">
+        <x:v>EMPIRE_ECHO_CORRIDOR</x:v>
+      </x:c>
+      <x:c r="B214" s="66" t="str">
+        <x:v>ICE_TUNNEL</x:v>
+      </x:c>
+      <x:c r="C214" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D214" s="66" t="str">
+        <x:v>Take the narrow maintenance tunnel above the corridor.</x:v>
+      </x:c>
+      <x:c r="E214" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F214" s="66" t="str">
+        <x:v>You emerge behind the stormtrooper position.</x:v>
+      </x:c>
+      <x:c r="G214" s="66" t="str">
+        <x:v>Falling ice gives away the tunnel exit.</x:v>
+      </x:c>
+      <x:c r="H214" s="73" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I214" s="73" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J214" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K214" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L214" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M214" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N214" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O214" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P214" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" ht="48" customHeight="1">
+      <x:c r="A215" s="66" t="str">
+        <x:v>EMPIRE_ECHO_CORRIDOR</x:v>
+      </x:c>
+      <x:c r="B215" s="66" t="str">
+        <x:v>FIRE_STEAM</x:v>
+      </x:c>
+      <x:c r="C215" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D215" s="66" t="str">
+        <x:v>Shoot a frozen pipe and gamble that it vents across the enemy.</x:v>
+      </x:c>
+      <x:c r="E215" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F215" s="66" t="str">
+        <x:v>Steam blinds the stormtrooper without blocking Luke.</x:v>
+      </x:c>
+      <x:c r="G215" s="66" t="str">
+        <x:v>The pipe vents across your own route.</x:v>
+      </x:c>
+      <x:c r="H215" s="73" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I215" s="73" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J215" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K215" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L215" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M215" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N215" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O215" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P215" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" ht="48" customHeight="1">
+      <x:c r="A216" s="66" t="str">
+        <x:v>EMPIRE_ECHO_CORRIDOR</x:v>
+      </x:c>
+      <x:c r="B216" s="66" t="str">
+        <x:v>READ_HELMET</x:v>
+      </x:c>
+      <x:c r="C216" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D216" s="66" t="str">
+        <x:v>Watch the helmet movement to anticipate the squad's targeting calls.</x:v>
+      </x:c>
+      <x:c r="E216" s="73" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F216" s="66" t="str">
+        <x:v>You identify the next firing lane before it forms.</x:v>
+      </x:c>
+      <x:c r="G216" s="66" t="str">
+        <x:v>A false head turn sends you into the shot.</x:v>
+      </x:c>
+      <x:c r="H216" s="73" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="I216" s="73" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J216" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K216" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L216" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M216" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N216" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O216" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P216" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" ht="48" customHeight="1">
+      <x:c r="A217" s="66" t="str">
+        <x:v>FLASHGORDON_SKY_CITY</x:v>
+      </x:c>
+      <x:c r="B217" s="66" t="str">
+        <x:v>HOLD_BRIDGE</x:v>
+      </x:c>
+      <x:c r="C217" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D217" s="66" t="str">
+        <x:v>Hold the landing bridge in place as the platforms separate.</x:v>
+      </x:c>
+      <x:c r="E217" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F217" s="66" t="str">
+        <x:v>The bridge stays aligned and corners the Hawkman before Flash.</x:v>
+      </x:c>
+      <x:c r="G217" s="66" t="str">
+        <x:v>The bridge twists free and leaves you exposed.</x:v>
+      </x:c>
+      <x:c r="H217" s="73" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="I217" s="73" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J217" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K217" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L217" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M217" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N217" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O217" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P217" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" ht="48" customHeight="1">
+      <x:c r="A218" s="66" t="str">
+        <x:v>FLASHGORDON_SKY_CITY</x:v>
+      </x:c>
+      <x:c r="B218" s="66" t="str">
+        <x:v>FACE_WIND</x:v>
+      </x:c>
+      <x:c r="C218" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D218" s="66" t="str">
+        <x:v>Advance into the violent crosswind without surrendering ground.</x:v>
+      </x:c>
+      <x:c r="E218" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F218" s="66" t="str">
+        <x:v>You endure the gusts and keep the Hawkman's attention.</x:v>
+      </x:c>
+      <x:c r="G218" s="66" t="str">
+        <x:v>The wind drives you back toward the platform edge.</x:v>
+      </x:c>
+      <x:c r="H218" s="73" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I218" s="73" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J218" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K218" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L218" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M218" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N218" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O218" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P218" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" ht="48" customHeight="1">
+      <x:c r="A219" s="66" t="str">
+        <x:v>FLASHGORDON_SKY_CITY</x:v>
+      </x:c>
+      <x:c r="B219" s="66" t="str">
+        <x:v>SWING_CHAIN</x:v>
+      </x:c>
+      <x:c r="C219" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D219" s="66" t="str">
+        <x:v>Swing beneath the bridge and climb behind the winged warrior.</x:v>
+      </x:c>
+      <x:c r="E219" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F219" s="66" t="str">
+        <x:v>You clear the open air and reach his blind side.</x:v>
+      </x:c>
+      <x:c r="G219" s="66" t="str">
+        <x:v>The chain jerks and the Hawkman spots you.</x:v>
+      </x:c>
+      <x:c r="H219" s="73" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I219" s="73" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J219" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K219" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L219" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M219" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N219" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O219" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P219" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" ht="48" customHeight="1">
+      <x:c r="A220" s="66" t="str">
+        <x:v>FLASHGORDON_SKY_CITY</x:v>
+      </x:c>
+      <x:c r="B220" s="66" t="str">
+        <x:v>JUMP_GLIDER</x:v>
+      </x:c>
+      <x:c r="C220" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D220" s="66" t="str">
+        <x:v>Leap onto an unmanned glider and trust its controls.</x:v>
+      </x:c>
+      <x:c r="E220" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F220" s="66" t="str">
+        <x:v>The glider carries you directly across the champion's path.</x:v>
+      </x:c>
+      <x:c r="G220" s="66" t="str">
+        <x:v>It banks toward the imperial guns instead.</x:v>
+      </x:c>
+      <x:c r="H220" s="73" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I220" s="73" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J220" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K220" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L220" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M220" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N220" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O220" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P220" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" ht="48" customHeight="1">
+      <x:c r="A221" s="66" t="str">
+        <x:v>FLASHGORDON_SKY_CITY</x:v>
+      </x:c>
+      <x:c r="B221" s="66" t="str">
+        <x:v>WATCH_FEATHERS</x:v>
+      </x:c>
+      <x:c r="C221" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D221" s="66" t="str">
+        <x:v>Read the Hawkman's wing feathers to predict his next dive.</x:v>
+      </x:c>
+      <x:c r="E221" s="73" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F221" s="66" t="str">
+        <x:v>The feather angle reveals the attack before he commits.</x:v>
+      </x:c>
+      <x:c r="G221" s="66" t="str">
+        <x:v>A sudden gust changes the dive at the last moment.</x:v>
+      </x:c>
+      <x:c r="H221" s="73" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="I221" s="73" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J221" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K221" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L221" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M221" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N221" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O221" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P221" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" ht="48" customHeight="1">
+      <x:c r="A222" s="66" t="str">
+        <x:v>WILLOW_NOCKMAAR_GATE</x:v>
+      </x:c>
+      <x:c r="B222" s="66" t="str">
+        <x:v>TURN_WINCH</x:v>
+      </x:c>
+      <x:c r="C222" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D222" s="66" t="str">
+        <x:v>Turn the gate winch against its locking mechanism.</x:v>
+      </x:c>
+      <x:c r="E222" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F222" s="66" t="str">
+        <x:v>The chain moves and blocks the soldier's advance.</x:v>
+      </x:c>
+      <x:c r="G222" s="66" t="str">
+        <x:v>The winch catches and signals the guard.</x:v>
+      </x:c>
+      <x:c r="H222" s="73" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="I222" s="73" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J222" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K222" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L222" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M222" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N222" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O222" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P222" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" ht="48" customHeight="1">
+      <x:c r="A223" s="66" t="str">
+        <x:v>WILLOW_NOCKMAAR_GATE</x:v>
+      </x:c>
+      <x:c r="B223" s="66" t="str">
+        <x:v>HOLD_PORTCULLIS</x:v>
+      </x:c>
+      <x:c r="C223" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D223" s="66" t="str">
+        <x:v>Hold the descending portcullis while Willow passes beneath it.</x:v>
+      </x:c>
+      <x:c r="E223" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F223" s="66" t="str">
+        <x:v>You endure the weight and keep the route open.</x:v>
+      </x:c>
+      <x:c r="G223" s="66" t="str">
+        <x:v>The iron teeth force you to release it.</x:v>
+      </x:c>
+      <x:c r="H223" s="73" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I223" s="73" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J223" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K223" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L223" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M223" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N223" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O223" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P223" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="48" customHeight="1">
+      <x:c r="A224" s="66" t="str">
+        <x:v>WILLOW_NOCKMAAR_GATE</x:v>
+      </x:c>
+      <x:c r="B224" s="66" t="str">
+        <x:v>CLIMB_CHAIN</x:v>
+      </x:c>
+      <x:c r="C224" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D224" s="66" t="str">
+        <x:v>Climb the gate chain and enter through the upper mechanism.</x:v>
+      </x:c>
+      <x:c r="E224" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F224" s="66" t="str">
+        <x:v>You reach the stair above the soldier.</x:v>
+      </x:c>
+      <x:c r="G224" s="66" t="str">
+        <x:v>The chain swings against the stone and alerts him.</x:v>
+      </x:c>
+      <x:c r="H224" s="73" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I224" s="73" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J224" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K224" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L224" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M224" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N224" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O224" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P224" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" ht="48" customHeight="1">
+      <x:c r="A225" s="66" t="str">
+        <x:v>WILLOW_NOCKMAAR_GATE</x:v>
+      </x:c>
+      <x:c r="B225" s="66" t="str">
+        <x:v>USE_ACORN</x:v>
+      </x:c>
+      <x:c r="C225" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D225" s="66" t="str">
+        <x:v>Cast an enchanted acorn at the gate and trust what it transforms.</x:v>
+      </x:c>
+      <x:c r="E225" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F225" s="66" t="str">
+        <x:v>The locking bar turns to stone and snaps under its own weight.</x:v>
+      </x:c>
+      <x:c r="G225" s="66" t="str">
+        <x:v>The acorn transforms a harmless support instead.</x:v>
+      </x:c>
+      <x:c r="H225" s="73" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I225" s="73" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="J225" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K225" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L225" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M225" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N225" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O225" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P225" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" ht="48" customHeight="1">
+      <x:c r="A226" s="66" t="str">
+        <x:v>WILLOW_NOCKMAAR_GATE</x:v>
+      </x:c>
+      <x:c r="B226" s="66" t="str">
+        <x:v>READ_CREST</x:v>
+      </x:c>
+      <x:c r="C226" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D226" s="66" t="str">
+        <x:v>Study the guard crests to identify the captain's control key.</x:v>
+      </x:c>
+      <x:c r="E226" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F226" s="66" t="str">
+        <x:v>The correct insignia reveals which key opens the gate.</x:v>
+      </x:c>
+      <x:c r="G226" s="66" t="str">
+        <x:v>A ceremonial crest points to the wrong ring.</x:v>
+      </x:c>
+      <x:c r="H226" s="73" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="I226" s="73" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="J226" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K226" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L226" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M226" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N226" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O226" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P226" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" ht="48" customHeight="1">
+      <x:c r="A227" s="66" t="str">
+        <x:v>LABYRINTH_GOBLIN_PATROL</x:v>
+      </x:c>
+      <x:c r="B227" s="66" t="str">
+        <x:v>MOVE_WALL</x:v>
+      </x:c>
+      <x:c r="C227" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D227" s="66" t="str">
+        <x:v>Push the rotating wall before the goblin seals the passage.</x:v>
+      </x:c>
+      <x:c r="E227" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F227" s="66" t="str">
+        <x:v>The wall turns and traps the guard on Sarah's side.</x:v>
+      </x:c>
+      <x:c r="G227" s="66" t="str">
+        <x:v>The mechanism reverses and opens beside him.</x:v>
+      </x:c>
+      <x:c r="H227" s="73" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="I227" s="73" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J227" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K227" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L227" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M227" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N227" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O227" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P227" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" ht="48" customHeight="1">
+      <x:c r="A228" s="66" t="str">
+        <x:v>LABYRINTH_GOBLIN_PATROL</x:v>
+      </x:c>
+      <x:c r="B228" s="66" t="str">
+        <x:v>IGNORE_RIDDLES</x:v>
+      </x:c>
+      <x:c r="C228" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D228" s="66" t="str">
+        <x:v>Keep walking as the corridor repeats the same taunts and turns.</x:v>
+      </x:c>
+      <x:c r="E228" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F228" s="66" t="str">
+        <x:v>You resist the maze and maintain the true direction.</x:v>
+      </x:c>
+      <x:c r="G228" s="66" t="str">
+        <x:v>The repetition breaks your focus and the guard catches up.</x:v>
+      </x:c>
+      <x:c r="H228" s="73" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I228" s="73" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J228" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K228" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L228" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M228" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N228" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O228" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P228" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" ht="48" customHeight="1">
+      <x:c r="A229" s="66" t="str">
+        <x:v>LABYRINTH_GOBLIN_PATROL</x:v>
+      </x:c>
+      <x:c r="B229" s="66" t="str">
+        <x:v>CLIMB_DOORS</x:v>
+      </x:c>
+      <x:c r="C229" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D229" s="66" t="str">
+        <x:v>Climb the stacked doorframes and cross above the patrol.</x:v>
+      </x:c>
+      <x:c r="E229" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F229" s="66" t="str">
+        <x:v>You descend behind the Goblin Guard.</x:v>
+      </x:c>
+      <x:c r="G229" s="66" t="str">
+        <x:v>A painted door swings open beneath your hand.</x:v>
+      </x:c>
+      <x:c r="H229" s="73" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I229" s="73" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J229" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K229" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L229" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M229" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N229" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O229" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P229" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" ht="48" customHeight="1">
+      <x:c r="A230" s="66" t="str">
+        <x:v>LABYRINTH_GOBLIN_PATROL</x:v>
+      </x:c>
+      <x:c r="B230" s="66" t="str">
+        <x:v>CHOOSE_KNOCKER</x:v>
+      </x:c>
+      <x:c r="C230" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D230" s="66" t="str">
+        <x:v>Use one of two arguing door knockers without resolving which tells the truth.</x:v>
+      </x:c>
+      <x:c r="E230" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F230" s="66" t="str">
+        <x:v>The chosen door opens onto the guard's blind side.</x:v>
+      </x:c>
+      <x:c r="G230" s="66" t="str">
+        <x:v>It opens directly in front of his patrol.</x:v>
+      </x:c>
+      <x:c r="H230" s="73" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I230" s="73" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="J230" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K230" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L230" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M230" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N230" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O230" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P230" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" ht="48" customHeight="1">
+      <x:c r="A231" s="66" t="str">
+        <x:v>LABYRINTH_GOBLIN_PATROL</x:v>
+      </x:c>
+      <x:c r="B231" s="66" t="str">
+        <x:v>FOLLOW_CHALK</x:v>
+      </x:c>
+      <x:c r="C231" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D231" s="66" t="str">
+        <x:v>Separate Sarah's chalk marks from the copies made by the maze.</x:v>
+      </x:c>
+      <x:c r="E231" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F231" s="66" t="str">
+        <x:v>The smudged original reveals the real route.</x:v>
+      </x:c>
+      <x:c r="G231" s="66" t="str">
+        <x:v>A perfect imitation leads toward the guard.</x:v>
+      </x:c>
+      <x:c r="H231" s="73" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="I231" s="73" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="J231" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K231" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L231" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M231" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N231" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O231" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P231" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" ht="48" customHeight="1">
+      <x:c r="A232" s="66" t="str">
+        <x:v>TRON_DISC_ARENA</x:v>
+      </x:c>
+      <x:c r="B232" s="66" t="str">
+        <x:v>BREAK_WALL</x:v>
+      </x:c>
+      <x:c r="C232" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D232" s="66" t="str">
+        <x:v>Drive a disc into the arena wall until its code fractures.</x:v>
+      </x:c>
+      <x:c r="E232" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F232" s="66" t="str">
+        <x:v>The wall opens and limits Sark's movement.</x:v>
+      </x:c>
+      <x:c r="G232" s="66" t="str">
+        <x:v>The disc rebounds into his attack path.</x:v>
+      </x:c>
+      <x:c r="H232" s="73" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I232" s="73" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J232" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K232" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L232" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M232" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N232" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O232" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P232" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" ht="48" customHeight="1">
+      <x:c r="A233" s="66" t="str">
+        <x:v>TRON_DISC_ARENA</x:v>
+      </x:c>
+      <x:c r="B233" s="66" t="str">
+        <x:v>ABSORB_IMPACT</x:v>
+      </x:c>
+      <x:c r="C233" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D233" s="66" t="str">
+        <x:v>Take Sark's first disc impact and keep Flynn's platform active.</x:v>
+      </x:c>
+      <x:c r="E233" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F233" s="66" t="str">
+        <x:v>You remain coherent and preserve the platform.</x:v>
+      </x:c>
+      <x:c r="G233" s="66" t="str">
+        <x:v>The impact destabilizes your code.</x:v>
+      </x:c>
+      <x:c r="H233" s="73" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="I233" s="73" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J233" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K233" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L233" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M233" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N233" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O233" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P233" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" ht="48" customHeight="1">
+      <x:c r="A234" s="66" t="str">
+        <x:v>TRON_DISC_ARENA</x:v>
+      </x:c>
+      <x:c r="B234" s="66" t="str">
+        <x:v>JUMP_GRID</x:v>
+      </x:c>
+      <x:c r="C234" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D234" s="66" t="str">
+        <x:v>Leap between disappearing grid squares and reach Sark's platform.</x:v>
+      </x:c>
+      <x:c r="E234" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F234" s="66" t="str">
+        <x:v>You cross before the sequence resets.</x:v>
+      </x:c>
+      <x:c r="G234" s="66" t="str">
+        <x:v>A square vanishes beneath your landing.</x:v>
+      </x:c>
+      <x:c r="H234" s="73" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="I234" s="73" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J234" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K234" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L234" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M234" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N234" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O234" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P234" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" ht="48" customHeight="1">
+      <x:c r="A235" s="66" t="str">
+        <x:v>TRON_DISC_ARENA</x:v>
+      </x:c>
+      <x:c r="B235" s="66" t="str">
+        <x:v>THROW_BANK</x:v>
+      </x:c>
+      <x:c r="C235" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D235" s="66" t="str">
+        <x:v>Bank a disc off an untested wall angle.</x:v>
+      </x:c>
+      <x:c r="E235" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F235" s="66" t="str">
+        <x:v>The ricochet strikes Sark from outside his guard.</x:v>
+      </x:c>
+      <x:c r="G235" s="66" t="str">
+        <x:v>The angle returns the disc toward you.</x:v>
+      </x:c>
+      <x:c r="H235" s="73" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="I235" s="73" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J235" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K235" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L235" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M235" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N235" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O235" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P235" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="48" customHeight="1">
+      <x:c r="A236" s="66" t="str">
+        <x:v>TRON_DISC_ARENA</x:v>
+      </x:c>
+      <x:c r="B236" s="66" t="str">
+        <x:v>READ_PATTERN</x:v>
+      </x:c>
+      <x:c r="C236" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D236" s="66" t="str">
+        <x:v>Study the arena pulse to predict which grid squares will remain.</x:v>
+      </x:c>
+      <x:c r="E236" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F236" s="66" t="str">
+        <x:v>The pattern reveals a stable path to Sark.</x:v>
+      </x:c>
+      <x:c r="G236" s="66" t="str">
+        <x:v>The MCP changes the sequence after you commit.</x:v>
+      </x:c>
+      <x:c r="H236" s="73" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="I236" s="73" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J236" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K236" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L236" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M236" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N236" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O236" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P236" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" ht="48" customHeight="1">
+      <x:c r="A237" s="66" t="str">
+        <x:v>ARMYDARKNESS_GRAVEYARD</x:v>
+      </x:c>
+      <x:c r="B237" s="66" t="str">
+        <x:v>SLAM_COFFIN</x:v>
+      </x:c>
+      <x:c r="C237" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D237" s="66" t="str">
+        <x:v>Slam a coffin lid across the Deadite's path.</x:v>
+      </x:c>
+      <x:c r="E237" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F237" s="66" t="str">
+        <x:v>The lid pins the warrior long enough for Ash to aim.</x:v>
+      </x:c>
+      <x:c r="G237" s="66" t="str">
+        <x:v>The rotten wood bursts apart in your hands.</x:v>
+      </x:c>
+      <x:c r="H237" s="73" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I237" s="73" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J237" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K237" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L237" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M237" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N237" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O237" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P237" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" ht="48" customHeight="1">
+      <x:c r="A238" s="66" t="str">
+        <x:v>ARMYDARKNESS_GRAVEYARD</x:v>
+      </x:c>
+      <x:c r="B238" s="66" t="str">
+        <x:v>IGNORE_BITE</x:v>
+      </x:c>
+      <x:c r="C238" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D238" s="66" t="str">
+        <x:v>Hold the Deadite back despite its claws and teeth.</x:v>
+      </x:c>
+      <x:c r="E238" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F238" s="66" t="str">
+        <x:v>You keep it occupied and refuse to release your grip.</x:v>
+      </x:c>
+      <x:c r="G238" s="66" t="str">
+        <x:v>Its relentless attack breaks your hold.</x:v>
+      </x:c>
+      <x:c r="H238" s="73" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="I238" s="73" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J238" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K238" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L238" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M238" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N238" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O238" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P238" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" ht="48" customHeight="1">
+      <x:c r="A239" s="66" t="str">
+        <x:v>ARMYDARKNESS_GRAVEYARD</x:v>
+      </x:c>
+      <x:c r="B239" s="66" t="str">
+        <x:v>SWING_SHOVEL</x:v>
+      </x:c>
+      <x:c r="C239" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D239" s="66" t="str">
+        <x:v>Vault a gravestone and seize the shovel behind the Deadite.</x:v>
+      </x:c>
+      <x:c r="E239" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F239" s="66" t="str">
+        <x:v>You land with the weapon at its exposed back.</x:v>
+      </x:c>
+      <x:c r="G239" s="66" t="str">
+        <x:v>The stone tips and drops you into the grave.</x:v>
+      </x:c>
+      <x:c r="H239" s="73" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="I239" s="73" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J239" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K239" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L239" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M239" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N239" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O239" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P239" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" ht="48" customHeight="1">
+      <x:c r="A240" s="66" t="str">
+        <x:v>ARMYDARKNESS_GRAVEYARD</x:v>
+      </x:c>
+      <x:c r="B240" s="66" t="str">
+        <x:v>RECITE_WORDS</x:v>
+      </x:c>
+      <x:c r="C240" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D240" s="66" t="str">
+        <x:v>Recite the half-remembered burial phrase and hope it is close enough.</x:v>
+      </x:c>
+      <x:c r="E240" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F240" s="66" t="str">
+        <x:v>The ground grips the Deadite's legs and halts it.</x:v>
+      </x:c>
+      <x:c r="G240" s="66" t="str">
+        <x:v>The wrong words awaken another burst of movement.</x:v>
+      </x:c>
+      <x:c r="H240" s="73" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="I240" s="73" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J240" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K240" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L240" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M240" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N240" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O240" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P240" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" ht="48" customHeight="1">
+      <x:c r="A241" s="66" t="str">
+        <x:v>ARMYDARKNESS_GRAVEYARD</x:v>
+      </x:c>
+      <x:c r="B241" s="66" t="str">
+        <x:v>CHECK_SHADOW</x:v>
+      </x:c>
+      <x:c r="C241" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D241" s="66" t="str">
+        <x:v>Use the moonlight to distinguish the moving corpse from the still ones.</x:v>
+      </x:c>
+      <x:c r="E241" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F241" s="66" t="str">
+        <x:v>The wrong shadow reveals the Deadite before it lunges.</x:v>
+      </x:c>
+      <x:c r="G241" s="66" t="str">
+        <x:v>A swaying branch creates a convincing false target.</x:v>
+      </x:c>
+      <x:c r="H241" s="73" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="I241" s="73" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J241" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K241" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L241" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M241" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N241" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O241" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P241" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" ht="48" customHeight="1">
+      <x:c r="A242" s="66" t="str">
+        <x:v>STARGATE_TEMPLE_GATE</x:v>
+      </x:c>
+      <x:c r="B242" s="66" t="str">
+        <x:v>TOPPLE_COLUMN</x:v>
+      </x:c>
+      <x:c r="C242" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D242" s="66" t="str">
+        <x:v>Topple a cracked column across the guard's route.</x:v>
+      </x:c>
+      <x:c r="E242" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F242" s="66" t="str">
+        <x:v>The column falls and traps the Horus Guard in the courtyard.</x:v>
+      </x:c>
+      <x:c r="G242" s="66" t="str">
+        <x:v>The stone turns and falls away from the target.</x:v>
+      </x:c>
+      <x:c r="H242" s="73" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="I242" s="73" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J242" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K242" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L242" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M242" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N242" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O242" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P242" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" ht="48" customHeight="1">
+      <x:c r="A243" s="66" t="str">
+        <x:v>STARGATE_TEMPLE_GATE</x:v>
+      </x:c>
+      <x:c r="B243" s="66" t="str">
+        <x:v>CROSS_STAFF_FIRE</x:v>
+      </x:c>
+      <x:c r="C243" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D243" s="66" t="str">
+        <x:v>Advance through staff blasts while Daniel reaches the glyphs.</x:v>
+      </x:c>
+      <x:c r="E243" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F243" s="66" t="str">
+        <x:v>You endure the fire and keep the guard focused on you.</x:v>
+      </x:c>
+      <x:c r="G243" s="66" t="str">
+        <x:v>The barrage halts you short of the doorway.</x:v>
+      </x:c>
+      <x:c r="H243" s="73" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="I243" s="73" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J243" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K243" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L243" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M243" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N243" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O243" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P243" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" ht="48" customHeight="1">
+      <x:c r="A244" s="66" t="str">
+        <x:v>STARGATE_TEMPLE_GATE</x:v>
+      </x:c>
+      <x:c r="B244" s="66" t="str">
+        <x:v>CLIMB_STATUE</x:v>
+      </x:c>
+      <x:c r="C244" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D244" s="66" t="str">
+        <x:v>Climb the temple statue and descend behind the guard.</x:v>
+      </x:c>
+      <x:c r="E244" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F244" s="66" t="str">
+        <x:v>You land beyond the helmet's field of view.</x:v>
+      </x:c>
+      <x:c r="G244" s="66" t="str">
+        <x:v>Loose ornament crashes into the courtyard.</x:v>
+      </x:c>
+      <x:c r="H244" s="73" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="I244" s="73" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J244" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K244" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L244" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M244" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N244" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O244" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P244" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" ht="48" customHeight="1">
+      <x:c r="A245" s="66" t="str">
+        <x:v>STARGATE_TEMPLE_GATE</x:v>
+      </x:c>
+      <x:c r="B245" s="66" t="str">
+        <x:v>PRESS_SYMBOL</x:v>
+      </x:c>
+      <x:c r="C245" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D245" s="66" t="str">
+        <x:v>Press an unknown wall symbol and gamble that it controls the gate.</x:v>
+      </x:c>
+      <x:c r="E245" s="73" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F245" s="66" t="str">
+        <x:v>The gate shifts and separates the guard from reinforcements.</x:v>
+      </x:c>
+      <x:c r="G245" s="66" t="str">
+        <x:v>The symbol activates a warning beacon.</x:v>
+      </x:c>
+      <x:c r="H245" s="73" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="I245" s="73" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J245" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K245" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L245" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M245" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N245" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O245" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P245" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" ht="48" customHeight="1">
+      <x:c r="A246" s="66" t="str">
+        <x:v>STARGATE_TEMPLE_GATE</x:v>
+      </x:c>
+      <x:c r="B246" s="66" t="str">
+        <x:v>TRANSLATE_COMMAND</x:v>
+      </x:c>
+      <x:c r="C246" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D246" s="66" t="str">
+        <x:v>Translate the cartouche on the guard's control bracer.</x:v>
+      </x:c>
+      <x:c r="E246" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F246" s="66" t="str">
+        <x:v>You identify the symbol that interrupts its weapon.</x:v>
+      </x:c>
+      <x:c r="G246" s="66" t="str">
+        <x:v>A ceremonial inscription conceals the real command.</x:v>
+      </x:c>
+      <x:c r="H246" s="73" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="I246" s="73" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J246" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K246" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L246" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M246" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N246" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O246" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P246" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" ht="48" customHeight="1">
+      <x:c r="A247" s="66" t="str">
+        <x:v>EXCALIBUR_BLACK_BRIDGE</x:v>
+      </x:c>
+      <x:c r="B247" s="66" t="str">
+        <x:v>BREAK_LANCE</x:v>
+      </x:c>
+      <x:c r="C247" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D247" s="66" t="str">
+        <x:v>Catch the lowered lance and break it against the bridge rail.</x:v>
+      </x:c>
+      <x:c r="E247" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F247" s="66" t="str">
+        <x:v>The shaft splits and Arthur advances into the opening.</x:v>
+      </x:c>
+      <x:c r="G247" s="66" t="str">
+        <x:v>The lance drives you backward across the stones.</x:v>
+      </x:c>
+      <x:c r="H247" s="73" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="I247" s="73" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J247" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K247" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L247" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M247" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N247" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O247" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P247" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" ht="48" customHeight="1">
+      <x:c r="A248" s="66" t="str">
+        <x:v>EXCALIBUR_BLACK_BRIDGE</x:v>
+      </x:c>
+      <x:c r="B248" s="66" t="str">
+        <x:v>HOLD_CROSSING</x:v>
+      </x:c>
+      <x:c r="C248" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D248" s="66" t="str">
+        <x:v>Stand in the center of the bridge and absorb the knight's charge.</x:v>
+      </x:c>
+      <x:c r="E248" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F248" s="66" t="str">
+        <x:v>You withstand the impact and halt the armored horse.</x:v>
+      </x:c>
+      <x:c r="G248" s="66" t="str">
+        <x:v>The charge carries you toward the edge.</x:v>
+      </x:c>
+      <x:c r="H248" s="73" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="I248" s="73" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J248" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K248" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L248" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M248" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N248" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O248" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P248" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" ht="48" customHeight="1">
+      <x:c r="A249" s="66" t="str">
+        <x:v>EXCALIBUR_BLACK_BRIDGE</x:v>
+      </x:c>
+      <x:c r="B249" s="66" t="str">
+        <x:v>VAULT_RAIL</x:v>
+      </x:c>
+      <x:c r="C249" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D249" s="66" t="str">
+        <x:v>Vault the bridge rail and return behind the Black Knight.</x:v>
+      </x:c>
+      <x:c r="E249" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F249" s="66" t="str">
+        <x:v>You land beyond the lance point and divide his guard.</x:v>
+      </x:c>
+      <x:c r="G249" s="66" t="str">
+        <x:v>Wet stone ruins the landing.</x:v>
+      </x:c>
+      <x:c r="H249" s="73" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="I249" s="73" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J249" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K249" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L249" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M249" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N249" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O249" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P249" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250" ht="48" customHeight="1">
+      <x:c r="A250" s="66" t="str">
+        <x:v>EXCALIBUR_BLACK_BRIDGE</x:v>
+      </x:c>
+      <x:c r="B250" s="66" t="str">
+        <x:v>CHALLENGE_OATH</x:v>
+      </x:c>
+      <x:c r="C250" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D250" s="66" t="str">
+        <x:v>Invoke an old knightly oath and gamble that he still honors it.</x:v>
+      </x:c>
+      <x:c r="E250" s="73" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F250" s="66" t="str">
+        <x:v>The knight hesitates and lowers his shield to answer.</x:v>
+      </x:c>
+      <x:c r="G250" s="66" t="str">
+        <x:v>He recognizes no authority in the words.</x:v>
+      </x:c>
+      <x:c r="H250" s="73" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="I250" s="73" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J250" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K250" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L250" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M250" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N250" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O250" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P250" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251" ht="48" customHeight="1">
+      <x:c r="A251" s="66" t="str">
+        <x:v>EXCALIBUR_BLACK_BRIDGE</x:v>
+      </x:c>
+      <x:c r="B251" s="66" t="str">
+        <x:v>READ_HERALDRY</x:v>
+      </x:c>
+      <x:c r="C251" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D251" s="66" t="str">
+        <x:v>Study the damaged heraldry for the battle that broke his confidence.</x:v>
+      </x:c>
+      <x:c r="E251" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F251" s="66" t="str">
+        <x:v>The crest reveals which feint he expects.</x:v>
+      </x:c>
+      <x:c r="G251" s="66" t="str">
+        <x:v>The marks belong to armor taken from another knight.</x:v>
+      </x:c>
+      <x:c r="H251" s="73" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="I251" s="73" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J251" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K251" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L251" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M251" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N251" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O251" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P251" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252" ht="48" customHeight="1">
+      <x:c r="A252" s="66" t="str">
+        <x:v>DUNE_SARDAUKAR_RAID</x:v>
+      </x:c>
+      <x:c r="B252" s="66" t="str">
+        <x:v>SHIFT_WRECK</x:v>
+      </x:c>
+      <x:c r="C252" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D252" s="66" t="str">
+        <x:v>Shift the ornithopter wreckage into the Sardaukar's descent.</x:v>
+      </x:c>
+      <x:c r="E252" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F252" s="66" t="str">
+        <x:v>The metal slides and forces the trooper into Paul's reach.</x:v>
+      </x:c>
+      <x:c r="G252" s="66" t="str">
+        <x:v>The wreck settles deeper into the sand.</x:v>
+      </x:c>
+      <x:c r="H252" s="73" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="I252" s="73" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J252" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K252" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L252" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M252" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N252" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O252" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P252" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253" ht="48" customHeight="1">
+      <x:c r="A253" s="66" t="str">
+        <x:v>DUNE_SARDAUKAR_RAID</x:v>
+      </x:c>
+      <x:c r="B253" s="66" t="str">
+        <x:v>CONTROL_WATER</x:v>
+      </x:c>
+      <x:c r="C253" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D253" s="66" t="str">
+        <x:v>Control your breathing and movement through the exhausting heat.</x:v>
+      </x:c>
+      <x:c r="E253" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F253" s="66" t="str">
+        <x:v>You conserve strength and hold the line beside Paul.</x:v>
+      </x:c>
+      <x:c r="G253" s="66" t="str">
+        <x:v>The heat drains your reactions before the attack.</x:v>
+      </x:c>
+      <x:c r="H253" s="73" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="I253" s="73" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J253" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K253" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L253" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M253" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N253" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O253" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P253" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254" ht="48" customHeight="1">
+      <x:c r="A254" s="66" t="str">
+        <x:v>DUNE_SARDAUKAR_RAID</x:v>
+      </x:c>
+      <x:c r="B254" s="66" t="str">
+        <x:v>SANDWALK_FLANK</x:v>
+      </x:c>
+      <x:c r="C254" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D254" s="66" t="str">
+        <x:v>Use an irregular sandwalk to circle beyond the trooper's sight.</x:v>
+      </x:c>
+      <x:c r="E254" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F254" s="66" t="str">
+        <x:v>You reach the flank without creating a readable rhythm.</x:v>
+      </x:c>
+      <x:c r="G254" s="66" t="str">
+        <x:v>One repeated step reveals your path.</x:v>
+      </x:c>
+      <x:c r="H254" s="73" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="I254" s="73" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="J254" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K254" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L254" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M254" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N254" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O254" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P254" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" ht="48" customHeight="1">
+      <x:c r="A255" s="66" t="str">
+        <x:v>DUNE_SARDAUKAR_RAID</x:v>
+      </x:c>
+      <x:c r="B255" s="66" t="str">
+        <x:v>TRUST_VISION</x:v>
+      </x:c>
+      <x:c r="C255" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D255" s="66" t="str">
+        <x:v>Follow a brief prescient image without knowing which future it belongs to.</x:v>
+      </x:c>
+      <x:c r="E255" s="73" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F255" s="66" t="str">
+        <x:v>The vision leads you through the blade's exact opening.</x:v>
+      </x:c>
+      <x:c r="G255" s="66" t="str">
+        <x:v>The possible future dissolves as you commit.</x:v>
+      </x:c>
+      <x:c r="H255" s="73" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="I255" s="73" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J255" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K255" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L255" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M255" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N255" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O255" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P255" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" ht="48" customHeight="1">
+      <x:c r="A256" s="66" t="str">
+        <x:v>DUNE_SARDAUKAR_RAID</x:v>
+      </x:c>
+      <x:c r="B256" s="66" t="str">
+        <x:v>READ_BLADE</x:v>
+      </x:c>
+      <x:c r="C256" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D256" s="66" t="str">
+        <x:v>Watch the Sardaukar's blade angle for the killing feint.</x:v>
+      </x:c>
+      <x:c r="E256" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F256" s="66" t="str">
+        <x:v>You identify the hidden second strike and warn Paul.</x:v>
+      </x:c>
+      <x:c r="G256" s="66" t="str">
+        <x:v>The trooper changes grip inside the motion.</x:v>
+      </x:c>
+      <x:c r="H256" s="73" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="I256" s="73" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J256" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K256" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L256" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M256" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N256" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O256" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P256" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd05973ff05a4d3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d62d0a8b1704962"/>
   </x:tableParts>
 </x:worksheet>
 </file>
